--- a/Employee_Reports_wi48/Christian Archie Barbosa Niez Q0364.xlsx
+++ b/Employee_Reports_wi48/Christian Archie Barbosa Niez Q0364.xlsx
@@ -569,11 +569,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -618,11 +618,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -667,11 +667,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -716,11 +716,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -765,11 +765,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -814,11 +814,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -863,11 +863,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -912,11 +912,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -961,11 +961,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1010,11 +1010,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1059,11 +1059,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1108,11 +1108,11 @@
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1157,11 +1157,11 @@
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1206,11 +1206,11 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1255,11 +1255,11 @@
         </is>
       </c>
       <c r="H17" s="3" t="n">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1304,11 +1304,11 @@
         </is>
       </c>
       <c r="H18" s="3" t="n">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -1353,11 +1353,11 @@
         </is>
       </c>
       <c r="H19" s="3" t="n">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1402,11 +1402,11 @@
         </is>
       </c>
       <c r="H20" s="3" t="n">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -1451,11 +1451,11 @@
         </is>
       </c>
       <c r="H21" s="3" t="n">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -1501,11 +1501,11 @@
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-81</v>
+        <v>-84</v>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
@@ -1550,11 +1550,11 @@
         </is>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-480</v>
+        <v>-483</v>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
@@ -1599,11 +1599,11 @@
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-124</v>
+        <v>-127</v>
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
@@ -1648,11 +1648,11 @@
         </is>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-84</v>
+        <v>-87</v>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
@@ -1697,11 +1697,11 @@
         </is>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-124</v>
+        <v>-127</v>
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr">
@@ -1720,9 +1720,21 @@
           <t>Procedure For Handling New or Unfamilliar Task (SOPs)</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr"/>
-      <c r="D27" s="4" t="inlineStr"/>
-      <c r="E27" s="4" t="inlineStr"/>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>IMS</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>LSME-IMS-SOP-022</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>SOP</t>
+        </is>
+      </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
           <t>22-Apr-2025</t>
@@ -1734,11 +1746,11 @@
         </is>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-82</v>
+        <v>-85</v>
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
@@ -1783,11 +1795,11 @@
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-83</v>
+        <v>-86</v>
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
@@ -1832,11 +1844,11 @@
         </is>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-70</v>
+        <v>-73</v>
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
@@ -1869,11 +1881,11 @@
         </is>
       </c>
       <c r="H30" s="3" t="n">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
@@ -2459,7 +2471,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7565</v>
+        <v>7562</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
